--- a/results_OV3heads_mmdec_pixeldec_only_decoder_1xA6000_11_8M_epoch17_lr_1e-3.xlsx
+++ b/results_OV3heads_mmdec_pixeldec_only_decoder_1xA6000_11_8M_epoch17_lr_1e-3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,6 +525,27 @@
       </c>
       <c r="E5" t="n">
         <v>63.59999847412109</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>iSAIDDataset</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>96.02999877929688</v>
+      </c>
+      <c r="D6" t="n">
+        <v>26.27000045776367</v>
+      </c>
+      <c r="E6" t="n">
+        <v>45.13000106811523</v>
       </c>
     </row>
   </sheetData>
